--- a/analysis/human_rating/calibration.xlsx
+++ b/analysis/human_rating/calibration.xlsx
@@ -513,7 +513,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="139" customHeight="1">
       <c r="A2" t="n">
         <v>1</v>
       </c>
@@ -550,7 +550,7 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
-    <row r="3">
+    <row r="3" ht="154" customHeight="1">
       <c r="A3" t="n">
         <v>2</v>
       </c>
@@ -593,7 +593,7 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
     </row>
-    <row r="4">
+    <row r="4" ht="154" customHeight="1">
       <c r="A4" t="n">
         <v>3</v>
       </c>
@@ -634,7 +634,7 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
     </row>
-    <row r="5">
+    <row r="5" ht="139" customHeight="1">
       <c r="A5" t="n">
         <v>4</v>
       </c>
@@ -673,7 +673,7 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
     </row>
-    <row r="6">
+    <row r="6" ht="154" customHeight="1">
       <c r="A6" t="n">
         <v>5</v>
       </c>
@@ -716,7 +716,7 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
     </row>
-    <row r="7">
+    <row r="7" ht="139" customHeight="1">
       <c r="A7" t="n">
         <v>6</v>
       </c>
@@ -753,7 +753,7 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
     </row>
-    <row r="8">
+    <row r="8" ht="124" customHeight="1">
       <c r="A8" t="n">
         <v>7</v>
       </c>
@@ -792,7 +792,7 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
     </row>
-    <row r="9">
+    <row r="9" ht="139" customHeight="1">
       <c r="A9" t="n">
         <v>8</v>
       </c>
@@ -829,7 +829,7 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
     </row>
-    <row r="10">
+    <row r="10" ht="124" customHeight="1">
       <c r="A10" t="n">
         <v>9</v>
       </c>
@@ -866,7 +866,7 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
     </row>
-    <row r="11">
+    <row r="11" ht="154" customHeight="1">
       <c r="A11" t="n">
         <v>10</v>
       </c>
@@ -907,7 +907,7 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
     </row>
-    <row r="12">
+    <row r="12" ht="154" customHeight="1">
       <c r="A12" t="n">
         <v>11</v>
       </c>
@@ -948,7 +948,7 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
     </row>
-    <row r="13">
+    <row r="13" ht="184" customHeight="1">
       <c r="A13" t="n">
         <v>12</v>
       </c>
@@ -985,7 +985,7 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
     </row>
-    <row r="14">
+    <row r="14" ht="184" customHeight="1">
       <c r="A14" t="n">
         <v>13</v>
       </c>
@@ -1022,7 +1022,7 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
     </row>
-    <row r="15">
+    <row r="15" ht="184" customHeight="1">
       <c r="A15" t="n">
         <v>14</v>
       </c>
@@ -1059,7 +1059,7 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
     </row>
-    <row r="16">
+    <row r="16" ht="124" customHeight="1">
       <c r="A16" t="n">
         <v>15</v>
       </c>
@@ -1096,7 +1096,7 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
     </row>
-    <row r="17">
+    <row r="17" ht="124" customHeight="1">
       <c r="A17" t="n">
         <v>16</v>
       </c>
@@ -1133,7 +1133,7 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
     </row>
-    <row r="18">
+    <row r="18" ht="139" customHeight="1">
       <c r="A18" t="n">
         <v>17</v>
       </c>
@@ -1172,7 +1172,7 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
     </row>
-    <row r="19">
+    <row r="19" ht="139" customHeight="1">
       <c r="A19" t="n">
         <v>18</v>
       </c>
@@ -1209,7 +1209,7 @@
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
     </row>
-    <row r="20">
+    <row r="20" ht="139" customHeight="1">
       <c r="A20" t="n">
         <v>19</v>
       </c>
@@ -1246,7 +1246,7 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
     </row>
-    <row r="21">
+    <row r="21" ht="139" customHeight="1">
       <c r="A21" t="n">
         <v>20</v>
       </c>
@@ -1285,7 +1285,7 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
     </row>
-    <row r="22">
+    <row r="22" ht="184" customHeight="1">
       <c r="A22" t="n">
         <v>21</v>
       </c>
@@ -1324,7 +1324,7 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
     </row>
-    <row r="23">
+    <row r="23" ht="139" customHeight="1">
       <c r="A23" t="n">
         <v>22</v>
       </c>
@@ -1362,7 +1362,7 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
     </row>
-    <row r="24">
+    <row r="24" ht="124" customHeight="1">
       <c r="A24" t="n">
         <v>23</v>
       </c>
@@ -1400,7 +1400,7 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
     </row>
-    <row r="25">
+    <row r="25" ht="139" customHeight="1">
       <c r="A25" t="n">
         <v>24</v>
       </c>
@@ -1439,7 +1439,7 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
     </row>
-    <row r="26">
+    <row r="26" ht="184" customHeight="1">
       <c r="A26" t="n">
         <v>25</v>
       </c>
@@ -1478,7 +1478,7 @@
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
     </row>
-    <row r="27">
+    <row r="27" ht="154" customHeight="1">
       <c r="A27" t="n">
         <v>26</v>
       </c>
@@ -1519,7 +1519,7 @@
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
     </row>
-    <row r="28">
+    <row r="28" ht="139" customHeight="1">
       <c r="A28" t="n">
         <v>27</v>
       </c>
@@ -1557,7 +1557,7 @@
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
     </row>
-    <row r="29">
+    <row r="29" ht="139" customHeight="1">
       <c r="A29" t="n">
         <v>28</v>
       </c>
@@ -1594,7 +1594,7 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
     </row>
-    <row r="30">
+    <row r="30" ht="199" customHeight="1">
       <c r="A30" t="n">
         <v>29</v>
       </c>
@@ -1636,7 +1636,7 @@
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
     </row>
-    <row r="31">
+    <row r="31" ht="124" customHeight="1">
       <c r="A31" t="n">
         <v>30</v>
       </c>

--- a/analysis/human_rating/calibration.xlsx
+++ b/analysis/human_rating/calibration.xlsx
@@ -513,30 +513,30 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="139" customHeight="1">
+    <row r="2" ht="214" customHeight="1">
       <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>R8bf2aa63</t>
+          <t>Rc5654e5b</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Issue: Communication tactics
-Sub-issue: Frequent or repeated calls
-Complaint: I setup payment arrangements with this company and after arrangements were made phone calls started stating they would not accept the payment method I have. So after arrangements were made they sent me a letter stating they cancelled the arrangements and have continued to call me daily 4-5 times a day. I ca n't afcord to spend more money then what was agreed to in order to make the payments and they keep insisting that its my responsibility to change my payment methods in order for them to accept the payments.</t>
+          <t>Issue: False statements or representation
+Sub-issue: Indicated shouldn't respond to lawsuit
+Complaint: for medical debt, I was given a summons and showed up in court. Their lawyer worked out a " deal '' with me where I could pay payments and if defaulted would have a judgement against me. I singed the paper and paid my payments. I have proof of payments. They still went back to court and claimed I stopped paying and got a judgement against me. I was not sent any paperwork to show up in court. I am filing something to get a judge to look at it again. I called and they admitted they " misapplied '' my payments but said it does n't stop their process. They are now garnishing me over twice the amount I agreed to pay in court. And I did n't break the agreement! They would n't work with me before it went to court at all. They wanted all or nothing and I could n't afford to pay it, so they took me to court. This is Credit Service Company inc. in XXXX XXXX, CO.</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>I’m really sorry to hear about the frustration you’ve experienced with the frequent calls and the confusion around your payment arrangements. I want to reassure you that I’m here to help resolve this for you. I will immediately reach out to our payment processing team to clarify your arrangements and ensure that the calls stop while we sort this out. You deserve clear communication and peace of mind, and I appreciate your patience as we work on this.</t>
+          <t>I’m truly sorry to hear about the difficulties you’ve faced, and I understand how frustrating this situation must be for you. I want to assure you that we take your concerns seriously and will work to resolve this matter. I will escalate your case to our dispute resolution team right away so they can look into the misapplied payments and the garnishment issue. You deserve clarity and support, and we’re here to help.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -550,35 +550,33 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
     </row>
-    <row r="3" ht="154" customHeight="1">
+    <row r="3" ht="199" customHeight="1">
       <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R60145ed1</t>
+          <t>Rc8c3a332</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>997</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>Issue: Repossession
-Sub-issue: Company explaining amount owed
-Complaint: The company can not explain what the amount owed is. I have received various letters with various amounts. 
-They have incorrectly reported to credit bureaus the amount of late days. 
-They have incorrectly reported the amount owed to credit bureaus. 
-They have disabled my account preventing me from seeing late fees vs amount owed on the vehicle. 
-The company counts late days cumulative and not consecutive so although payments were made to catch up the marked the payments months behind.</t>
+          <t>Issue: Incorrect information on your report
+Sub-issue: Account information incorrect
+Complaint: I contacted Synchrony regarding a charge off from Amazon in an attempt to settle the account. 
+After speaking to a representative, I was told a 1099-C had been issued and the debt had been forgiven, so no payments could be made on the account. Synchrony continued to report the balance as {$1000.00} owed even with a 1099-C issued and telling me that I was not allowed to make payments on the account. 
+How is it possible a balance is owed yet Im not allowed to make payments on it because the balance has been forgiven? I have disputed through the CRAs and Synchrony continues to report the balance as {$1000.00}</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>Acknowledgement: I understand that you are experiencing issues with the company’s explanation of the amount owed, discrepancies in credit reporting, and restrictions on your account access.  
-Next step: We will review your account information and the concerns you've raised, and aim to provide you with a detailed response within 10 business days.  
+          <t>Acknowledgement: We understand that you are frustrated with the reporting of a balance on your account despite having been informed that a 1099-C was issued and the debt was forgiven.  
+Next step: We will investigate the reporting of your account and review the information related to the 1099-C, and you can expect an update within 15 business days.  
 What we need from you: Nothing at this time.</t>
         </is>
       </c>
@@ -593,34 +591,32 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
     </row>
-    <row r="4" ht="154" customHeight="1">
+    <row r="4" ht="199" customHeight="1">
       <c r="A4" t="n">
         <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R7853349d</t>
+          <t>Rab39c7d2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>997</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>Issue: Repossession
-Sub-issue: Company explaining amount owed
-Complaint: The company can not explain what the amount owed is. I have received various letters with various amounts. 
-They have incorrectly reported to credit bureaus the amount of late days. 
-They have incorrectly reported the amount owed to credit bureaus. 
-They have disabled my account preventing me from seeing late fees vs amount owed on the vehicle. 
-The company counts late days cumulative and not consecutive so although payments were made to catch up the marked the payments months behind.</t>
+          <t>Issue: Incorrect information on your report
+Sub-issue: Account information incorrect
+Complaint: I contacted Synchrony regarding a charge off from Amazon in an attempt to settle the account. 
+After speaking to a representative, I was told a 1099-C had been issued and the debt had been forgiven, so no payments could be made on the account. Synchrony continued to report the balance as {$1000.00} owed even with a 1099-C issued and telling me that I was not allowed to make payments on the account. 
+How is it possible a balance is owed yet Im not allowed to make payments on it because the balance has been forgiven? I have disputed through the CRAs and Synchrony continues to report the balance as {$1000.00}</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>I understand how frustrating it must be to receive conflicting information and to have your account access restricted. I want to assure you that we take your concerns seriously. I will escalate this issue to our account management team right away to get clarifications on the amount owed and the reporting to the credit bureaus. We will do our best to resolve this for you and keep you updated on the progress. Thank you for your patience as we work to address these issues.</t>
+          <t>I understand how frustrating this situation must be for you, and I want to make sure we address your concerns. I appreciate you bringing this to our attention, and I’ll escalate your issue to our account review team for further investigation. They will look into the reporting discrepancies you mentioned and get back to you soon. Thank you for your patience as we work to resolve this matter.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -634,31 +630,31 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
     </row>
-    <row r="5" ht="139" customHeight="1">
+    <row r="5" ht="109" customHeight="1">
       <c r="A5" t="n">
         <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R7430997e</t>
+          <t>Ref0f42a3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>Issue: Communication tactics
-Sub-issue: Frequent or repeated calls
-Complaint: I am filing this complaint regarding a collection account that I have no knowledge of. The debt collector has been repeatedly contacting me by phone and mail attempting to collect on this account. I have already informed them that I do not recognize this account and requested that they stop contacting me. Despite my request, they continue to call and send collection notices demanding payment. I do not believe this debt belongs to me, and their continued attempts to collect are causing unnecessary stress and harassment.</t>
+          <t>Issue: Repossession
+Sub-issue: Loan balance remaining after the vehicle is repossessed and sold
+Complaint: The car was repossessed and when we contacted the company they explained the car was sold, but they are still charging us for the car. Im requesting that this be removed from my credit report immediately. The cars value was {$8000.00} and they repossessed the car for {$2000.00} so its no longer my debt.</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>Acknowledgement: I understand that you are frustrated by the frequent calls and mail from a debt collector regarding an account you do not recognize.  
-Next step: I will escalate your complaint to our collections department for further review and they will reach out to you within the next three business days.  
+          <t>Acknowledgement: I understand that you are frustrated about the remaining loan balance after the repossession and sale of your vehicle.  
+Next step: I will review your account and the details surrounding the repossession, and I will provide you with an update within five business days.  
 What we need from you: Nothing at this time.</t>
         </is>
       </c>
@@ -673,35 +669,33 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
     </row>
-    <row r="6" ht="154" customHeight="1">
+    <row r="6" ht="199" customHeight="1">
       <c r="A6" t="n">
         <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ra83f44e1</t>
+          <t>R3bcfcb8f</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>997</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>Issue: Repossession
-Sub-issue: Company explaining amount owed
-Complaint: The company can not explain what the amount owed is. I have received various letters with various amounts. 
-They have incorrectly reported to credit bureaus the amount of late days. 
-They have incorrectly reported the amount owed to credit bureaus. 
-They have disabled my account preventing me from seeing late fees vs amount owed on the vehicle. 
-The company counts late days cumulative and not consecutive so although payments were made to catch up the marked the payments months behind.</t>
+          <t>Issue: Incorrect information on your report
+Sub-issue: Account information incorrect
+Complaint: I contacted Synchrony regarding a charge off from Amazon in an attempt to settle the account. 
+After speaking to a representative, I was told a 1099-C had been issued and the debt had been forgiven, so no payments could be made on the account. Synchrony continued to report the balance as {$1000.00} owed even with a 1099-C issued and telling me that I was not allowed to make payments on the account. 
+How is it possible a balance is owed yet Im not allowed to make payments on it because the balance has been forgiven? I have disputed through the CRAs and Synchrony continues to report the balance as {$1000.00}</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>Acknowledgement: I understand that you are frustrated with the unclear amount owed, the discrepancies in the credit reporting, and that your account access has been restricted.  
-Next step: I will escalate your concerns to our account review team, who will investigate the situation and reach out to you within the next five business days.  
+          <t>Acknowledgement: I understand your frustration regarding the incorrect information reported on your account, especially after being told that the debt was forgiven.  
+Next step: I will escalate your concern to our account review team to ensure they investigate the reporting of your account, and you can expect to hear back from us within 7 business days.  
 What we need from you: Nothing at this time.</t>
         </is>
       </c>
@@ -716,30 +710,30 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
     </row>
-    <row r="7" ht="139" customHeight="1">
+    <row r="7" ht="109" customHeight="1">
       <c r="A7" t="n">
         <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R3e8550e0</t>
+          <t>Ref40d93c</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>Issue: Communication tactics
-Sub-issue: Frequent or repeated calls
-Complaint: I am filing this complaint regarding a collection account that I have no knowledge of. The debt collector has been repeatedly contacting me by phone and mail attempting to collect on this account. I have already informed them that I do not recognize this account and requested that they stop contacting me. Despite my request, they continue to call and send collection notices demanding payment. I do not believe this debt belongs to me, and their continued attempts to collect are causing unnecessary stress and harassment.</t>
+          <t>Issue: Repossession
+Sub-issue: Loan balance remaining after the vehicle is repossessed and sold
+Complaint: The car was repossessed and when we contacted the company they explained the car was sold, but they are still charging us for the car. Im requesting that this be removed from my credit report immediately. The cars value was {$8000.00} and they repossessed the car for {$2000.00} so its no longer my debt.</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>Hi there, I’m truly sorry to hear about the frustration and stress this situation has caused you. I want you to know that I take your concerns seriously, and I will personally look into this matter. As the next step, I'll escalate your complaint to our collections team to ensure they review your case and stop any further communication until it's resolved. Thank you for bringing this to our attention, and I appreciate your patience as we work to address it.</t>
+          <t>I’m really sorry to hear about the frustration you’re experiencing with your loan balance after the repossession. I understand how upsetting this situation can be, and I want to take ownership and assist you. I will escalate your concern to our credit reporting team to review your account and the details of the repossession. They will look into this further and get back to you as soon as possible. Thank you for your patience as we work through this together.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -753,31 +747,32 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
     </row>
-    <row r="8" ht="124" customHeight="1">
+    <row r="8" ht="334" customHeight="1">
       <c r="A8" t="n">
         <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R1b18a023</t>
+          <t>R35b4a665</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>Issue: Problem with a company's investigation into an existing problem
-Sub-issue: Was not notified of investigation status or results
-Complaint: PLEASE BLOCKED AND REMOVED. Please expedite the removal of the unauthorized accounts from my credit report at your earliest convenience. I did not initiate or authorize these accounts, and I am unaware of their origins. In accordance with USC 1681g, I am formally requesting their removal within the next 15 days. Enclosed are the pertinent documents for your thorough review and reference.</t>
+          <t>Issue: Took or threatened to take negative or legal action
+Sub-issue: Threatened to arrest you or take you to jail if you do not pay
+Complaint: XXXX I called my XXXX XXXX XXXX and was notified that a third group named Bayou View Solution has purchased my debt phone number XXXX. I had been contacting the older creditor XXXXXXXX XXXX XXXX for several months to update a wrong balance. I recently talked to them. In my past i put in a disputes for records. These peole are targeting covid victims. 
+XXXX I received a no caller ID call someone with the incorrect address claiming to serve me but provided me with the law firm contact XXXX. I called and was placed on a 10 minute hold. He said I was being sued for {$16000.00}. I was in shock knowing my consumer report I first thought it was fraud and Identity Theft. He then came back and said that he was wrong and it was the amount of {$6000.00} same incorrect balance as XXXX XXXX reported same debt which I had mentioned they sold to this group making threats in the middle of the afternoon while I am at work. The male was rude and did not provide me with his name nor allowed me to speak. He then hung up on me. Twice I called back 3 times. To file a complaint. He said let 's talk in court with the papers, I said this is a recorded line and I am asking his name and details about my account. He then said he wants to file a cease and desist. This was an alarm to me and this tactic is not fair. He also said this company had been looking for me but they could not reach me so they are now trying to serve me. He hung up and blocked my number as I asked for account information. I could [...]</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>Acknowledgement: We understand you’re frustrated that you haven’t received updates on the investigation into the unauthorized accounts on your credit report.
-Next step: We’ll review the documents you provided and follow up with you within 10 business days with the status of our findings.
+          <t>Acknowledgement: I’m sorry you’ve been contacted by Bayou View Solutions about a debt and that they’ve used threatening language, including claims of legal action, which must have been very upsetting.
+Next step: I’ll escalate this to our Fraud and Compliance team today to review the situation and contact Bayou View Solutions to request verification of the debt and proper documentation.
 What we need from you: Nothing at this time.</t>
         </is>
       </c>
@@ -792,30 +787,30 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
     </row>
-    <row r="9" ht="139" customHeight="1">
+    <row r="9" ht="109" customHeight="1">
       <c r="A9" t="n">
         <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R1921d57d</t>
+          <t>Rffb24bf3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>Issue: Communication tactics
-Sub-issue: Frequent or repeated calls
-Complaint: I am filing this complaint regarding a collection account that I have no knowledge of. The debt collector has been repeatedly contacting me by phone and mail attempting to collect on this account. I have already informed them that I do not recognize this account and requested that they stop contacting me. Despite my request, they continue to call and send collection notices demanding payment. I do not believe this debt belongs to me, and their continued attempts to collect are causing unnecessary stress and harassment.</t>
+          <t>Issue: Repossession
+Sub-issue: Loan balance remaining after the vehicle is repossessed and sold
+Complaint: The car was repossessed and when we contacted the company they explained the car was sold, but they are still charging us for the car. Im requesting that this be removed from my credit report immediately. The cars value was {$8000.00} and they repossessed the car for {$2000.00} so its no longer my debt.</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>We sincerely apologize for the repeated communications you've experienced regarding the collection account, which has understandably caused you stress. Please provide us with your contact details and any relevant information about the account, and we will promptly investigate the matter to ensure that our communication practices comply with your requests.</t>
+          <t>Thank you for reaching out regarding your concerns about the repossession and the remaining loan balance. I recommend reviewing your loan agreement for details on deficiency balance policies, and please provide any documentation so we can assist you in resolving this matter, including the potential impact on your credit report.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -829,30 +824,31 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
     </row>
-    <row r="10" ht="124" customHeight="1">
+    <row r="10" ht="334" customHeight="1">
       <c r="A10" t="n">
         <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rf9b166c7</t>
+          <t>R451cea28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>Issue: Problem with a company's investigation into an existing problem
-Sub-issue: Was not notified of investigation status or results
-Complaint: PLEASE BLOCKED AND REMOVED. Please expedite the removal of the unauthorized accounts from my credit report at your earliest convenience. I did not initiate or authorize these accounts, and I am unaware of their origins. In accordance with USC 1681g, I am formally requesting their removal within the next 15 days. Enclosed are the pertinent documents for your thorough review and reference.</t>
+          <t>Issue: Took or threatened to take negative or legal action
+Sub-issue: Threatened to arrest you or take you to jail if you do not pay
+Complaint: XXXX I called my XXXX XXXX XXXX and was notified that a third group named Bayou View Solution has purchased my debt phone number XXXX. I had been contacting the older creditor XXXXXXXX XXXX XXXX for several months to update a wrong balance. I recently talked to them. In my past i put in a disputes for records. These peole are targeting covid victims. 
+XXXX I received a no caller ID call someone with the incorrect address claiming to serve me but provided me with the law firm contact XXXX. I called and was placed on a 10 minute hold. He said I was being sued for {$16000.00}. I was in shock knowing my consumer report I first thought it was fraud and Identity Theft. He then came back and said that he was wrong and it was the amount of {$6000.00} same incorrect balance as XXXX XXXX reported same debt which I had mentioned they sold to this group making threats in the middle of the afternoon while I am at work. The male was rude and did not provide me with his name nor allowed me to speak. He then hung up on me. Twice I called back 3 times. To file a complaint. He said let 's talk in court with the papers, I said this is a recorded line and I am asking his name and details about my account. He then said he wants to file a cease and desist. This was an alarm to me and this tactic is not fair. He also said this company had been looking for me but they could not reach me so they are now trying to serve me. He hung up and blocked my number as I asked for account information. I could [...]</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>I completely understand how frustrating this situation must be for you, and I'm sorry for the lack of communication about the status of the investigation. I want to assure you that we take these matters seriously and I will personally ensure that your request is prioritized. I’ll follow up with our investigation team today and will make sure they are aware of your concerns regarding the unauthorized accounts. Thank you for your patience as we work to resolve this issue for you.</t>
+          <t>I’m really sorry to hear about the frustrating experience you've had with the calls and the way you were treated. It’s completely understandable that this situation has caused you a lot of stress. I want you to know that we take these matters seriously, and I will escalate your complaint to our compliance team right away to ensure they address the conduct you've described. We’re here to support you, and I appreciate your patience as we work to resolve this.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -866,34 +862,32 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
     </row>
-    <row r="11" ht="154" customHeight="1">
+    <row r="11" ht="199" customHeight="1">
       <c r="A11" t="n">
         <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R1605b745</t>
+          <t>Raebc4f22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>997</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>Issue: Repossession
-Sub-issue: Company explaining amount owed
-Complaint: The company can not explain what the amount owed is. I have received various letters with various amounts. 
-They have incorrectly reported to credit bureaus the amount of late days. 
-They have incorrectly reported the amount owed to credit bureaus. 
-They have disabled my account preventing me from seeing late fees vs amount owed on the vehicle. 
-The company counts late days cumulative and not consecutive so although payments were made to catch up the marked the payments months behind.</t>
+          <t>Issue: Incorrect information on your report
+Sub-issue: Account information incorrect
+Complaint: I contacted Synchrony regarding a charge off from Amazon in an attempt to settle the account. 
+After speaking to a representative, I was told a 1099-C had been issued and the debt had been forgiven, so no payments could be made on the account. Synchrony continued to report the balance as {$1000.00} owed even with a 1099-C issued and telling me that I was not allowed to make payments on the account. 
+How is it possible a balance is owed yet Im not allowed to make payments on it because the balance has been forgiven? I have disputed through the CRAs and Synchrony continues to report the balance as {$1000.00}</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>Thank you for bringing this to our attention. We sincerely apologize for the confusion and frustration caused by the discrepancies in your account. We take these concerns very seriously and will immediately review your account to clarify the amounts owed and correct any inaccuracies reported to the credit bureaus. Please allow us 5-7 business days to investigate and provide you with a detailed breakdown of the charges, including late fees and payment history. We will also ensure your account access is restored so you can monitor your payments moving forward.</t>
+          <t>Thank you for bringing this to our attention. We sincerely apologize for the confusion and frustration caused by the incorrect reporting of your account. We understand the importance of accurate information on credit reports and will investigate this matter immediately. Please allow us up to 30 days to resolve this issue and update the information with the credit bureaus.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -907,34 +901,32 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
     </row>
-    <row r="12" ht="154" customHeight="1">
+    <row r="12" ht="199" customHeight="1">
       <c r="A12" t="n">
         <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R8c999635</t>
+          <t>R21eca929</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>997</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>Issue: Repossession
-Sub-issue: Company explaining amount owed
-Complaint: The company can not explain what the amount owed is. I have received various letters with various amounts. 
-They have incorrectly reported to credit bureaus the amount of late days. 
-They have incorrectly reported the amount owed to credit bureaus. 
-They have disabled my account preventing me from seeing late fees vs amount owed on the vehicle. 
-The company counts late days cumulative and not consecutive so although payments were made to catch up the marked the payments months behind.</t>
+          <t>Issue: Incorrect information on your report
+Sub-issue: Account information incorrect
+Complaint: I contacted Synchrony regarding a charge off from Amazon in an attempt to settle the account. 
+After speaking to a representative, I was told a 1099-C had been issued and the debt had been forgiven, so no payments could be made on the account. Synchrony continued to report the balance as {$1000.00} owed even with a 1099-C issued and telling me that I was not allowed to make payments on the account. 
+How is it possible a balance is owed yet Im not allowed to make payments on it because the balance has been forgiven? I have disputed through the CRAs and Synchrony continues to report the balance as {$1000.00}</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>I’m really sorry to hear about your frustrations with the repossession and the confusing information you've received regarding the amounts owed. I understand how important this is to you, and I want to help clarify this situation. I’ll escalate your concerns to our team right away to ensure we take a closer look at your account and provide you with a clear breakdown of the amounts owed. We’ll also review the reports to the credit bureaus to correct any inaccuracies. Thank you for your patience as we work to resolve this matter.</t>
+          <t>I'm really sorry to hear about the confusion and frustration this has caused you—it's definitely not the experience we want for our customers. I want to take ownership of this issue and ensure we get to the bottom of it. I will escalate your case to our billing department right away to review your account and clarify the reporting discrepancy related to the 1099-C. We'll keep you updated on our progress and work towards a resolution as soon as possible. Thank you for your patience!</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -948,30 +940,30 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
     </row>
-    <row r="13" ht="184" customHeight="1">
+    <row r="13" ht="169" customHeight="1">
       <c r="A13" t="n">
         <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R37e3ec05</t>
+          <t>R03697545</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>Issue: Unable to get your credit report or credit score
-Sub-issue: Other problem getting your report or credit score
-Complaint: Received denial letter. I have not applied for a loan. called company was transferred to fraud dept at that time they were to busy to assist me. was given direct number received recording to call back. called back and was left hanging on line. I did purchase a car for my son XXXX XXXX but it was paid in cash. I used a XXXX, I do not pay large amounts in cash in case a problem arises like now. We started a loan app but did not complete, decided against having finance charges. I don't have a copy of a loan being submitted to any finance company in that paperwork. I am sending a copy of receipt and letter, which I received XXXX. I only have reference # as the app was denied. # XXXX</t>
+          <t>Issue: Closing on a mortgage
+Sub-issue: Delays with the closing process
+Complaint: I have a complaint from the credit bureau my ID restoration was hacked and stolen from the data breach attack. I lost my information and contact with account agent. I have a personal workers compensation complaints from the illness. I have been trying to get my insurance renewed with the account litigation on file with the account fraud. I want to pursue with a account take over compromised ID restoration for financial compromise of Government accounts. I have a suspension access of liability insurance dispute from my complaint. I have a email arbitration dispute that involves a error log in of account manager.</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>I’m really sorry to hear about the trouble you’ve experienced trying to get your credit report and the confusion surrounding your loan application. I completely understand how frustrating this must be. To help you resolve this, I’ll personally reach out to our fraud department to ensure they are aware of your situation and can assist you further. Please keep an eye out for updates from us soon. Thank you for your patience as we work through this together.</t>
+          <t>I truly understand how frustrating this situation is for you, and I want to assure you that we're here to help. I'm taking ownership of your concerns and will be reaching out to our mortgage team to investigate the delays in your closing process and ensure they are addressed promptly. Thank you for your patience as we work through this, and I’ll keep you updated on any progress we make.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -985,30 +977,30 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
     </row>
-    <row r="14" ht="184" customHeight="1">
+    <row r="14" ht="169" customHeight="1">
       <c r="A14" t="n">
         <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R0b37ddc6</t>
+          <t>Rc48a038f</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>Issue: Unable to get your credit report or credit score
-Sub-issue: Other problem getting your report or credit score
-Complaint: Received denial letter. I have not applied for a loan. called company was transferred to fraud dept at that time they were to busy to assist me. was given direct number received recording to call back. called back and was left hanging on line. I did purchase a car for my son XXXX XXXX but it was paid in cash. I used a XXXX, I do not pay large amounts in cash in case a problem arises like now. We started a loan app but did not complete, decided against having finance charges. I don't have a copy of a loan being submitted to any finance company in that paperwork. I am sending a copy of receipt and letter, which I received XXXX. I only have reference # as the app was denied. # XXXX</t>
+          <t>Issue: Closing on a mortgage
+Sub-issue: Delays with the closing process
+Complaint: I have a complaint from the credit bureau my ID restoration was hacked and stolen from the data breach attack. I lost my information and contact with account agent. I have a personal workers compensation complaints from the illness. I have been trying to get my insurance renewed with the account litigation on file with the account fraud. I want to pursue with a account take over compromised ID restoration for financial compromise of Government accounts. I have a suspension access of liability insurance dispute from my complaint. I have a email arbitration dispute that involves a error log in of account manager.</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>I’m sorry to hear about the frustration you’ve experienced. Please provide any additional documentation you have, such as the denial letter and receipt, so we can assist you further in resolving this issue.</t>
+          <t>I’m sorry to hear about the challenges you’re facing with your mortgage closing and identity theft issues. Please provide documentation of the fraud and any correspondence with your lender or insurance provider so we can assist you further in resolving these matters.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1022,30 +1014,30 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
     </row>
-    <row r="15" ht="184" customHeight="1">
+    <row r="15" ht="169" customHeight="1">
       <c r="A15" t="n">
         <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R083a4d02</t>
+          <t>R36ed32c5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>Issue: Unable to get your credit report or credit score
-Sub-issue: Other problem getting your report or credit score
-Complaint: Received denial letter. I have not applied for a loan. called company was transferred to fraud dept at that time they were to busy to assist me. was given direct number received recording to call back. called back and was left hanging on line. I did purchase a car for my son XXXX XXXX but it was paid in cash. I used a XXXX, I do not pay large amounts in cash in case a problem arises like now. We started a loan app but did not complete, decided against having finance charges. I don't have a copy of a loan being submitted to any finance company in that paperwork. I am sending a copy of receipt and letter, which I received XXXX. I only have reference # as the app was denied. # XXXX</t>
+          <t>Issue: Closing on a mortgage
+Sub-issue: Delays with the closing process
+Complaint: I have a complaint from the credit bureau my ID restoration was hacked and stolen from the data breach attack. I lost my information and contact with account agent. I have a personal workers compensation complaints from the illness. I have been trying to get my insurance renewed with the account litigation on file with the account fraud. I want to pursue with a account take over compromised ID restoration for financial compromise of Government accounts. I have a suspension access of liability insurance dispute from my complaint. I have a email arbitration dispute that involves a error log in of account manager.</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>I’m truly sorry for the frustration you’re experiencing in trying to obtain your credit report and score. It sounds like you've had a very challenging time, and I appreciate your patience. To get things moving, I'll personally follow up with our fraud department to ensure that your case is prioritized, and we will work to provide clarity on your credit situation. Thank you for sending the receipt and the denial letter; that will help us address this issue more effectively.</t>
+          <t>Thank you for reaching out and sharing your concerns. I understand how frustrating these delays and complications must be, especially given the serious nature of your situation. I want to assure you that we will take immediate action to help. I will review your account and reach out to the relevant departments to expedite the resolution of your mortgage closing and address the issues regarding your ID restoration. We’re here to support you, and I’ll ensure you receive the assistance you need.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -1059,30 +1051,32 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
     </row>
-    <row r="16" ht="124" customHeight="1">
+    <row r="16" ht="334" customHeight="1">
       <c r="A16" t="n">
         <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>R36a03095</t>
+          <t>R3c31f675</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>Issue: Problem with a company's investigation into an existing problem
-Sub-issue: Was not notified of investigation status or results
-Complaint: PLEASE BLOCKED AND REMOVED. Please expedite the removal of the unauthorized accounts from my credit report at your earliest convenience. I did not initiate or authorize these accounts, and I am unaware of their origins. In accordance with USC 1681g, I am formally requesting their removal within the next 15 days. Enclosed are the pertinent documents for your thorough review and reference.</t>
+          <t>Issue: Took or threatened to take negative or legal action
+Sub-issue: Threatened to arrest you or take you to jail if you do not pay
+Complaint: XXXX I called my XXXX XXXX XXXX and was notified that a third group named Bayou View Solution has purchased my debt phone number XXXX. I had been contacting the older creditor XXXXXXXX XXXX XXXX for several months to update a wrong balance. I recently talked to them. In my past i put in a disputes for records. These peole are targeting covid victims. 
+XXXX I received a no caller ID call someone with the incorrect address claiming to serve me but provided me with the law firm contact XXXX. I called and was placed on a 10 minute hold. He said I was being sued for {$16000.00}. I was in shock knowing my consumer report I first thought it was fraud and Identity Theft. He then came back and said that he was wrong and it was the amount of {$6000.00} same incorrect balance as XXXX XXXX reported same debt which I had mentioned they sold to this group making threats in the middle of the afternoon while I am at work. The male was rude and did not provide me with his name nor allowed me to speak. He then hung up on me. Twice I called back 3 times. To file a complaint. He said let 's talk in court with the papers, I said this is a recorded line and I am asking his name and details about my account. He then said he wants to file a cease and desist. This was an alarm to me and this tactic is not fair. He also said this company had been looking for me but they could not reach me so they are now trying to serve me. He hung up and blocked my number as I asked for account information. I could [...]</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>I'm really sorry to hear about the issues you're facing with the unauthorized accounts on your credit report. I understand how frustrating this situation can be, and I want to assure you that we take your concerns seriously. I will personally follow up on the status of the investigation today and ensure that the necessary actions are taken promptly. Please expect to receive an update from us within the next few days. Thank you for your patience as we work to resolve this for you.</t>
+          <t>Dear [Customer's Name],
+I’m truly sorry to hear about the distressing experience you’ve had with Bayou View Solution. It’s completely understandable to feel frustrated and alarmed by their behavior. I want to assure you that we take this matter seriously, and I will look into this situation immediately to gather more details about your case. One next step I will take is to escalate your complaint to our resolution team so they can assist you further and make sure your concerns are addressed properly. Thank you for bringing this to our attention, and we’ll work to resolve it as swiftly as possible.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -1096,30 +1090,31 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
     </row>
-    <row r="17" ht="124" customHeight="1">
+    <row r="17" ht="334" customHeight="1">
       <c r="A17" t="n">
         <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rbb53eb22</t>
+          <t>R3bd4c209</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>Issue: Problem with a company's investigation into an existing problem
-Sub-issue: Was not notified of investigation status or results
-Complaint: PLEASE BLOCKED AND REMOVED. Please expedite the removal of the unauthorized accounts from my credit report at your earliest convenience. I did not initiate or authorize these accounts, and I am unaware of their origins. In accordance with USC 1681g, I am formally requesting their removal within the next 15 days. Enclosed are the pertinent documents for your thorough review and reference.</t>
+          <t>Issue: Took or threatened to take negative or legal action
+Sub-issue: Threatened to arrest you or take you to jail if you do not pay
+Complaint: XXXX I called my XXXX XXXX XXXX and was notified that a third group named Bayou View Solution has purchased my debt phone number XXXX. I had been contacting the older creditor XXXXXXXX XXXX XXXX for several months to update a wrong balance. I recently talked to them. In my past i put in a disputes for records. These peole are targeting covid victims. 
+XXXX I received a no caller ID call someone with the incorrect address claiming to serve me but provided me with the law firm contact XXXX. I called and was placed on a 10 minute hold. He said I was being sued for {$16000.00}. I was in shock knowing my consumer report I first thought it was fraud and Identity Theft. He then came back and said that he was wrong and it was the amount of {$6000.00} same incorrect balance as XXXX XXXX reported same debt which I had mentioned they sold to this group making threats in the middle of the afternoon while I am at work. The male was rude and did not provide me with his name nor allowed me to speak. He then hung up on me. Twice I called back 3 times. To file a complaint. He said let 's talk in court with the papers, I said this is a recorded line and I am asking his name and details about my account. He then said he wants to file a cease and desist. This was an alarm to me and this tactic is not fair. He also said this company had been looking for me but they could not reach me so they are now trying to serve me. He hung up and blocked my number as I asked for account information. I could [...]</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>We sincerely apologize for the delay in resolving this matter and appreciate your patience. We will immediately escalate your request and ensure the unauthorized accounts are removed from your credit report within the next 15 days, as required by law.</t>
+          <t>I’m sorry to hear about your experience—threatening legal action without proper verification is unacceptable. Please document all calls, request written validation of the debt, and file complaints with the [CFPB](https://www.consumerfinance.gov/) and your state attorney general’s office.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -1133,31 +1128,31 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
     </row>
-    <row r="18" ht="139" customHeight="1">
+    <row r="18" ht="214" customHeight="1">
       <c r="A18" t="n">
         <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R991985b9</t>
+          <t>R3771f844</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>Issue: Communication tactics
-Sub-issue: Frequent or repeated calls
-Complaint: I setup payment arrangements with this company and after arrangements were made phone calls started stating they would not accept the payment method I have. So after arrangements were made they sent me a letter stating they cancelled the arrangements and have continued to call me daily 4-5 times a day. I ca n't afcord to spend more money then what was agreed to in order to make the payments and they keep insisting that its my responsibility to change my payment methods in order for them to accept the payments.</t>
+          <t>Issue: False statements or representation
+Sub-issue: Indicated shouldn't respond to lawsuit
+Complaint: for medical debt, I was given a summons and showed up in court. Their lawyer worked out a " deal '' with me where I could pay payments and if defaulted would have a judgement against me. I singed the paper and paid my payments. I have proof of payments. They still went back to court and claimed I stopped paying and got a judgement against me. I was not sent any paperwork to show up in court. I am filing something to get a judge to look at it again. I called and they admitted they " misapplied '' my payments but said it does n't stop their process. They are now garnishing me over twice the amount I agreed to pay in court. And I did n't break the agreement! They would n't work with me before it went to court at all. They wanted all or nothing and I could n't afford to pay it, so they took me to court. This is Credit Service Company inc. in XXXX XXXX, CO.</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>Acknowledgement: I understand that you are frustrated with the repeated calls and the cancellation of your payment arrangements, which were supposed to provide clarity and peace of mind.  
-Next step: I will escalate your concern to our customer service management team to review your payment arrangement and communication history, and you will receive an update from us within the next 48 hours.  
+          <t>Acknowledgement: I understand that you are frustrated because you feel a judgment was unfairly issued against you despite having paid your agreed-upon payments on time.  
+Next step: We will reach out to the relevant department to investigate your payment records and the communication regarding the judgment, and we aim to provide you with an update within five business days.  
 What we need from you: Nothing at this time.</t>
         </is>
       </c>
@@ -1172,30 +1167,30 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
     </row>
-    <row r="19" ht="139" customHeight="1">
+    <row r="19" ht="109" customHeight="1">
       <c r="A19" t="n">
         <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ra4cc7f0c</t>
+          <t>R7b7ba657</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>Issue: Communication tactics
-Sub-issue: Frequent or repeated calls
-Complaint: I am filing this complaint regarding a collection account that I have no knowledge of. The debt collector has been repeatedly contacting me by phone and mail attempting to collect on this account. I have already informed them that I do not recognize this account and requested that they stop contacting me. Despite my request, they continue to call and send collection notices demanding payment. I do not believe this debt belongs to me, and their continued attempts to collect are causing unnecessary stress and harassment.</t>
+          <t>Issue: Repossession
+Sub-issue: Loan balance remaining after the vehicle is repossessed and sold
+Complaint: The car was repossessed and when we contacted the company they explained the car was sold, but they are still charging us for the car. Im requesting that this be removed from my credit report immediately. The cars value was {$8000.00} and they repossessed the car for {$2000.00} so its no longer my debt.</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>Thank you for bringing this to our attention. We sincerely apologize for the repeated calls and notices regarding this account. We take your concerns seriously and will immediately instruct our team to cease all further communication with you regarding this matter. Please allow us to review your records and investigate this issue further. We will reach out to you once we have more information.</t>
+          <t>Thank you for reaching out regarding your repossession and remaining loan balance. We understand your concern and will review the details of your account to ensure accuracy. If there was an overpayment or remaining balance discrepancy, we’ll work to resolve it promptly. Please allow us 5-7 business days to investigate and provide a resolution.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -1209,30 +1204,30 @@
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
     </row>
-    <row r="20" ht="139" customHeight="1">
+    <row r="20" ht="214" customHeight="1">
       <c r="A20" t="n">
         <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R48d7e9be</t>
+          <t>Ra70c62b0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>Issue: Communication tactics
-Sub-issue: Frequent or repeated calls
-Complaint: I setup payment arrangements with this company and after arrangements were made phone calls started stating they would not accept the payment method I have. So after arrangements were made they sent me a letter stating they cancelled the arrangements and have continued to call me daily 4-5 times a day. I ca n't afcord to spend more money then what was agreed to in order to make the payments and they keep insisting that its my responsibility to change my payment methods in order for them to accept the payments.</t>
+          <t>Issue: False statements or representation
+Sub-issue: Indicated shouldn't respond to lawsuit
+Complaint: for medical debt, I was given a summons and showed up in court. Their lawyer worked out a " deal '' with me where I could pay payments and if defaulted would have a judgement against me. I singed the paper and paid my payments. I have proof of payments. They still went back to court and claimed I stopped paying and got a judgement against me. I was not sent any paperwork to show up in court. I am filing something to get a judge to look at it again. I called and they admitted they " misapplied '' my payments but said it does n't stop their process. They are now garnishing me over twice the amount I agreed to pay in court. And I did n't break the agreement! They would n't work with me before it went to court at all. They wanted all or nothing and I could n't afford to pay it, so they took me to court. This is Credit Service Company inc. in XXXX XXXX, CO.</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>We sincerely apologize for the frustration caused by our communication and payment arrangement process. Please contact us directly at [customer service number/email] so we can resolve this issue promptly and ensure your payments are accepted as agreed.</t>
+          <t>I’m sorry to hear about your experience with Credit Service Company Inc. You have valid concerns about their actions, and it’s important to document all communications and payments as you pursue legal recourse. I recommend consulting with a consumer protection attorney or filing a complaint with the Colorado Attorney General’s Office to address these unfair practices.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -1246,31 +1241,31 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
     </row>
-    <row r="21" ht="139" customHeight="1">
+    <row r="21" ht="109" customHeight="1">
       <c r="A21" t="n">
         <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rd881425b</t>
+          <t>Rc0332a59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>Issue: Communication tactics
-Sub-issue: Frequent or repeated calls
-Complaint: I am filing this complaint regarding a collection account that I have no knowledge of. The debt collector has been repeatedly contacting me by phone and mail attempting to collect on this account. I have already informed them that I do not recognize this account and requested that they stop contacting me. Despite my request, they continue to call and send collection notices demanding payment. I do not believe this debt belongs to me, and their continued attempts to collect are causing unnecessary stress and harassment.</t>
+          <t>Issue: Repossession
+Sub-issue: Loan balance remaining after the vehicle is repossessed and sold
+Complaint: The car was repossessed and when we contacted the company they explained the car was sold, but they are still charging us for the car. Im requesting that this be removed from my credit report immediately. The cars value was {$8000.00} and they repossessed the car for {$2000.00} so its no longer my debt.</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>**Acknowledgement:** We acknowledge your concern regarding repeated communications from a debt collector regarding an account you do not recognize.
-**Next step:** We will review your account and contact the debt collector to request they cease further communications while we investigate.
+          <t>**Acknowledgement:** We understand that you are concerned about ongoing charges related to a repossessed vehicle and its impact on your credit report.
+**Next step:** We will review your account and provide a response regarding the remaining balance and credit reporting within 15 business days.
 **What we need from you:** Nothing at this time.</t>
         </is>
       </c>
@@ -1285,32 +1280,32 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
     </row>
-    <row r="22" ht="184" customHeight="1">
+    <row r="22" ht="169" customHeight="1">
       <c r="A22" t="n">
         <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R14257067</t>
+          <t>R5e436118</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>Issue: Unable to get your credit report or credit score
-Sub-issue: Other problem getting your report or credit score
-Complaint: Received denial letter. I have not applied for a loan. called company was transferred to fraud dept at that time they were to busy to assist me. was given direct number received recording to call back. called back and was left hanging on line. I did purchase a car for my son XXXX XXXX but it was paid in cash. I used a XXXX, I do not pay large amounts in cash in case a problem arises like now. We started a loan app but did not complete, decided against having finance charges. I don't have a copy of a loan being submitted to any finance company in that paperwork. I am sending a copy of receipt and letter, which I received XXXX. I only have reference # as the app was denied. # XXXX</t>
+          <t>Issue: Closing on a mortgage
+Sub-issue: Delays with the closing process
+Complaint: I have a complaint from the credit bureau my ID restoration was hacked and stolen from the data breach attack. I lost my information and contact with account agent. I have a personal workers compensation complaints from the illness. I have been trying to get my insurance renewed with the account litigation on file with the account fraud. I want to pursue with a account take over compromised ID restoration for financial compromise of Government accounts. I have a suspension access of liability insurance dispute from my complaint. I have a email arbitration dispute that involves a error log in of account manager.</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>**Acknowledgement:** You received a denial letter and are unable to obtain your credit report or credit score due to difficulties contacting the fraud department.
-**Next step:** We will escalate this to our fraud team for review within 3 business days.
-**What we need from you:** Please provide any additional details or documentation you have regarding the denial letter or transaction.</t>
+          <t>Acknowledgement: You have expressed concerns about delays in the mortgage closing process due to issues with your identity restoration and account access.
+Next step: We will review your account and escalate your concerns to our dedicated team for further assistance within the next 5 business days.
+What we need from you: Please provide any relevant documentation or details regarding your identity restoration and account access issues at your earliest convenience.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -1324,31 +1319,30 @@
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
     </row>
-    <row r="23" ht="139" customHeight="1">
+    <row r="23" ht="109" customHeight="1">
       <c r="A23" t="n">
         <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R8faca829</t>
+          <t>Rd8eae53b</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>Issue: Communication tactics
-Sub-issue: Frequent or repeated calls
-Complaint: I am filing this complaint regarding a collection account that I have no knowledge of. The debt collector has been repeatedly contacting me by phone and mail attempting to collect on this account. I have already informed them that I do not recognize this account and requested that they stop contacting me. Despite my request, they continue to call and send collection notices demanding payment. I do not believe this debt belongs to me, and their continued attempts to collect are causing unnecessary stress and harassment.</t>
+          <t>Issue: Repossession
+Sub-issue: Loan balance remaining after the vehicle is repossessed and sold
+Complaint: The car was repossessed and when we contacted the company they explained the car was sold, but they are still charging us for the car. Im requesting that this be removed from my credit report immediately. The cars value was {$8000.00} and they repossessed the car for {$2000.00} so its no longer my debt.</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>Dear [Customer's Name],
-I’m really sorry to hear about the frustration you’re experiencing with the frequent calls and mail regarding a collection account you don’t recognize. I completely understand how stressful this situation must be for you, and I want to assure you that we take your concerns very seriously. I will personally reach out to the collection agency on your behalf to make sure they stop contacting you until this matter is resolved. Please let me know if there's anything else I can do to assist you.</t>
+          <t>Hi there, I understand how frustrating this situation must be for you, and I'm really sorry for the stress it has caused. I want to take ownership of this issue and help you resolve it. I will escalate your request regarding the remaining loan balance and the impact on your credit report to our management team right away. You can expect a follow-up from us within the next few days. Thank you for your patience.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1362,31 +1356,36 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
     </row>
-    <row r="24" ht="124" customHeight="1">
+    <row r="24" ht="334" customHeight="1">
       <c r="A24" t="n">
         <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Rfc19e6c1</t>
+          <t>R9bf82058</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>Issue: Problem with a company's investigation into an existing problem
-Sub-issue: Was not notified of investigation status or results
-Complaint: PLEASE BLOCKED AND REMOVED. Please expedite the removal of the unauthorized accounts from my credit report at your earliest convenience. I did not initiate or authorize these accounts, and I am unaware of their origins. In accordance with USC 1681g, I am formally requesting their removal within the next 15 days. Enclosed are the pertinent documents for your thorough review and reference.</t>
+          <t>Issue: Took or threatened to take negative or legal action
+Sub-issue: Threatened to arrest you or take you to jail if you do not pay
+Complaint: XXXX I called my XXXX XXXX XXXX and was notified that a third group named Bayou View Solution has purchased my debt phone number XXXX. I had been contacting the older creditor XXXXXXXX XXXX XXXX for several months to update a wrong balance. I recently talked to them. In my past i put in a disputes for records. These peole are targeting covid victims. 
+XXXX I received a no caller ID call someone with the incorrect address claiming to serve me but provided me with the law firm contact XXXX. I called and was placed on a 10 minute hold. He said I was being sued for {$16000.00}. I was in shock knowing my consumer report I first thought it was fraud and Identity Theft. He then came back and said that he was wrong and it was the amount of {$6000.00} same incorrect balance as XXXX XXXX reported same debt which I had mentioned they sold to this group making threats in the middle of the afternoon while I am at work. The male was rude and did not provide me with his name nor allowed me to speak. He then hung up on me. Twice I called back 3 times. To file a complaint. He said let 's talk in court with the papers, I said this is a recorded line and I am asking his name and details about my account. He then said he wants to file a cease and desist. This was an alarm to me and this tactic is not fair. He also said this company had been looking for me but they could not reach me so they are now trying to serve me. He hung up and blocked my number as I asked for account information. I could [...]</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
           <t>Dear [Customer's Name],
-Thank you for reaching out regarding your concern. We sincerely apologize for any frustration caused by the lack of communication during our investigation process. Please be assured that we are prioritizing your request for the removal of the unauthorized accounts and will keep you updated on our progress, ensuring a resolution within the specified timeframe. If you have any further questions or need additional assistance, feel free to contact us directly.</t>
+Thank you for bringing this matter to our attention. We take your concerns seriously, especially regarding the conduct of our representatives. Please rest assured that we will investigate this situation thoroughly, as we do not condone any aggressive or misleading communication tactics. We will reach out to you directly to gather more information and work towards resolving this issue effectively. Your experience is important to us, and we appreciate your patience while we address it. 
+Sincerely,  
+[Your Name]  
+[Your Position]  
+[Company Name]</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1400,31 +1399,31 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
     </row>
-    <row r="25" ht="139" customHeight="1">
+    <row r="25" ht="214" customHeight="1">
       <c r="A25" t="n">
         <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rb4de1579</t>
+          <t>Rcc3af518</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>Issue: Communication tactics
-Sub-issue: Frequent or repeated calls
-Complaint: I setup payment arrangements with this company and after arrangements were made phone calls started stating they would not accept the payment method I have. So after arrangements were made they sent me a letter stating they cancelled the arrangements and have continued to call me daily 4-5 times a day. I ca n't afcord to spend more money then what was agreed to in order to make the payments and they keep insisting that its my responsibility to change my payment methods in order for them to accept the payments.</t>
+          <t>Issue: False statements or representation
+Sub-issue: Indicated shouldn't respond to lawsuit
+Complaint: for medical debt, I was given a summons and showed up in court. Their lawyer worked out a " deal '' with me where I could pay payments and if defaulted would have a judgement against me. I singed the paper and paid my payments. I have proof of payments. They still went back to court and claimed I stopped paying and got a judgement against me. I was not sent any paperwork to show up in court. I am filing something to get a judge to look at it again. I called and they admitted they " misapplied '' my payments but said it does n't stop their process. They are now garnishing me over twice the amount I agreed to pay in court. And I did n't break the agreement! They would n't work with me before it went to court at all. They wanted all or nothing and I could n't afford to pay it, so they took me to court. This is Credit Service Company inc. in XXXX XXXX, CO.</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>Acknowledgement: We understand that you are experiencing frequent calls after setting up payment arrangements and have concerns about the cancellation of those arrangements.  
-Next step: We will review your account details and the communication history to address the frequent calls, and you can expect an update from us within the next five business days.  
+          <t>Acknowledgement: I understand that you are experiencing issues related to a judgment against you despite having made agreed-upon payments, and that you were not notified of court proceedings.  
+Next step: We will review your complaint and the associated documentation to investigate the circumstances surrounding your case by the end of the week.  
 What we need from you: Nothing at this time.</t>
         </is>
       </c>
@@ -1439,32 +1438,32 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
     </row>
-    <row r="26" ht="184" customHeight="1">
+    <row r="26" ht="169" customHeight="1">
       <c r="A26" t="n">
         <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R8ac96a28</t>
+          <t>R1d711121</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>Issue: Unable to get your credit report or credit score
-Sub-issue: Other problem getting your report or credit score
-Complaint: Received denial letter. I have not applied for a loan. called company was transferred to fraud dept at that time they were to busy to assist me. was given direct number received recording to call back. called back and was left hanging on line. I did purchase a car for my son XXXX XXXX but it was paid in cash. I used a XXXX, I do not pay large amounts in cash in case a problem arises like now. We started a loan app but did not complete, decided against having finance charges. I don't have a copy of a loan being submitted to any finance company in that paperwork. I am sending a copy of receipt and letter, which I received XXXX. I only have reference # as the app was denied. # XXXX</t>
+          <t>Issue: Closing on a mortgage
+Sub-issue: Delays with the closing process
+Complaint: I have a complaint from the credit bureau my ID restoration was hacked and stolen from the data breach attack. I lost my information and contact with account agent. I have a personal workers compensation complaints from the illness. I have been trying to get my insurance renewed with the account litigation on file with the account fraud. I want to pursue with a account take over compromised ID restoration for financial compromise of Government accounts. I have a suspension access of liability insurance dispute from my complaint. I have a email arbitration dispute that involves a error log in of account manager.</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>Acknowledgement: I understand that you've been facing difficulties accessing your credit report and score, and this situation has understandably caused you frustration.  
-Next step: We will investigate the issue regarding your credit report and the denial letter you received, and you can expect an update from us within 5 business days.  
-What we need from you: Please send us the receipt and the denial letter you mentioned, as this information will help us resolve your issue more effectively.</t>
+          <t>Acknowledgement: I understand that you are experiencing significant frustration due to delays in the mortgage closing process, as well as complications arising from identity theft and related issues with your accounts.  
+Next step: We will thoroughly review your account and the situation you've described, and a representative will reach out to you within the next two business days to discuss the matter further.  
+What we need from you: Nothing at this time.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -1478,34 +1477,32 @@
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
     </row>
-    <row r="27" ht="154" customHeight="1">
+    <row r="27" ht="199" customHeight="1">
       <c r="A27" t="n">
         <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R3bd67254</t>
+          <t>Reb947ce3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>9865</t>
+          <t>997</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>Issue: Repossession
-Sub-issue: Company explaining amount owed
-Complaint: The company can not explain what the amount owed is. I have received various letters with various amounts. 
-They have incorrectly reported to credit bureaus the amount of late days. 
-They have incorrectly reported the amount owed to credit bureaus. 
-They have disabled my account preventing me from seeing late fees vs amount owed on the vehicle. 
-The company counts late days cumulative and not consecutive so although payments were made to catch up the marked the payments months behind.</t>
+          <t>Issue: Incorrect information on your report
+Sub-issue: Account information incorrect
+Complaint: I contacted Synchrony regarding a charge off from Amazon in an attempt to settle the account. 
+After speaking to a representative, I was told a 1099-C had been issued and the debt had been forgiven, so no payments could be made on the account. Synchrony continued to report the balance as {$1000.00} owed even with a 1099-C issued and telling me that I was not allowed to make payments on the account. 
+How is it possible a balance is owed yet Im not allowed to make payments on it because the balance has been forgiven? I have disputed through the CRAs and Synchrony continues to report the balance as {$1000.00}</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>We sincerely apologize for the confusion you've experienced regarding the amount owed, as well as the discrepancies in the reporting to credit bureaus. Please contact our customer service team immediately so we can resolve these issues and clarify your account status; we appreciate your patience as we work to correct these errors.</t>
+          <t>We apologize for the frustration you've experienced regarding the incorrect reporting of your account balance. Please provide us with your contact information so we can investigate this matter further and ensure the accuracy of your report.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1519,31 +1516,35 @@
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
     </row>
-    <row r="28" ht="139" customHeight="1">
+    <row r="28" ht="214" customHeight="1">
       <c r="A28" t="n">
         <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R6f65a54f</t>
+          <t>Rc295b8b0</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>Issue: Communication tactics
-Sub-issue: Frequent or repeated calls
-Complaint: I setup payment arrangements with this company and after arrangements were made phone calls started stating they would not accept the payment method I have. So after arrangements were made they sent me a letter stating they cancelled the arrangements and have continued to call me daily 4-5 times a day. I ca n't afcord to spend more money then what was agreed to in order to make the payments and they keep insisting that its my responsibility to change my payment methods in order for them to accept the payments.</t>
+          <t>Issue: False statements or representation
+Sub-issue: Indicated shouldn't respond to lawsuit
+Complaint: for medical debt, I was given a summons and showed up in court. Their lawyer worked out a " deal '' with me where I could pay payments and if defaulted would have a judgement against me. I singed the paper and paid my payments. I have proof of payments. They still went back to court and claimed I stopped paying and got a judgement against me. I was not sent any paperwork to show up in court. I am filing something to get a judge to look at it again. I called and they admitted they " misapplied '' my payments but said it does n't stop their process. They are now garnishing me over twice the amount I agreed to pay in court. And I did n't break the agreement! They would n't work with me before it went to court at all. They wanted all or nothing and I could n't afford to pay it, so they took me to court. This is Credit Service Company inc. in XXXX XXXX, CO.</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>Dear [Consumer's Name],  
-Thank you for bringing your concerns to our attention. We sincerely apologize for the confusion and frustration caused by the repeated calls and the cancellation of your payment arrangements. It is our goal to work with you and ensure that the agreed-upon terms are honored. Please reach out to our customer service team directly at [contact information] so we can address this issue promptly and find a resolution that suits your needs.</t>
+          <t>Dear [Consumer's Name],
+Thank you for reaching out to us regarding your situation. We take your concerns seriously and want to assure you that we are committed to resolving this matter. Please provide us with all relevant documentation, including proof of payments and any correspondence you've had with our office. We'll conduct a thorough investigation into your case to address the misapplication of your payments and ensure that your rights are protected.
+Sincerely,  
+[Your Name]  
+Customer Service Team  
+Credit Service Company Inc.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -1557,30 +1558,30 @@
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
     </row>
-    <row r="29" ht="139" customHeight="1">
+    <row r="29" ht="214" customHeight="1">
       <c r="A29" t="n">
         <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>R9bda61ba</t>
+          <t>R63c53d2d</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>Issue: Communication tactics
-Sub-issue: Frequent or repeated calls
-Complaint: I setup payment arrangements with this company and after arrangements were made phone calls started stating they would not accept the payment method I have. So after arrangements were made they sent me a letter stating they cancelled the arrangements and have continued to call me daily 4-5 times a day. I ca n't afcord to spend more money then what was agreed to in order to make the payments and they keep insisting that its my responsibility to change my payment methods in order for them to accept the payments.</t>
+          <t>Issue: False statements or representation
+Sub-issue: Indicated shouldn't respond to lawsuit
+Complaint: for medical debt, I was given a summons and showed up in court. Their lawyer worked out a " deal '' with me where I could pay payments and if defaulted would have a judgement against me. I singed the paper and paid my payments. I have proof of payments. They still went back to court and claimed I stopped paying and got a judgement against me. I was not sent any paperwork to show up in court. I am filing something to get a judge to look at it again. I called and they admitted they " misapplied '' my payments but said it does n't stop their process. They are now garnishing me over twice the amount I agreed to pay in court. And I did n't break the agreement! They would n't work with me before it went to court at all. They wanted all or nothing and I could n't afford to pay it, so they took me to court. This is Credit Service Company inc. in XXXX XXXX, CO.</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>I’m really sorry this has been so frustrating for you—I can see how overwhelming the repeated calls and confusion over your payment arrangements must be. I’ll personally make sure this gets reviewed right away to find a solution that works for both you and the company. I’ll reach out to the relevant team today to pause the calls and clarify the issue, and I’ll follow up with you by [specific date, e.g., Friday] to share what we’ve found.</t>
+          <t>I’m truly sorry this has been such a frustrating and stressful experience for you. On behalf of our institution, I want to acknowledge that your payments were misapplied, and I take this situation seriously. I’ll personally escalate this to our internal team to review the garnishment and ensure it aligns with the agreement we made. Please allow me 24 hours to follow up with you directly on next steps.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
@@ -1594,31 +1595,31 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
     </row>
-    <row r="30" ht="199" customHeight="1">
+    <row r="30" ht="229" customHeight="1">
       <c r="A30" t="n">
         <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Re0ebe790</t>
+          <t>R393a8d91</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>Issue: Unable to get your credit report or credit score
-Sub-issue: Other problem getting your report or credit score
-Complaint: Received denial letter. I have not applied for a loan. called company was transferred to fraud dept at that time they were to busy to assist me. was given direct number received recording to call back. called back and was left hanging on line. I did purchase a car for my son XXXX XXXX but it was paid in cash. I used a XXXX, I do not pay large amounts in cash in case a problem arises like now. We started a loan app but did not complete, decided against having finance charges. I don't have a copy of a loan being submitted to any finance company in that paperwork. I am sending a copy of receipt and letter, which I received XXXX. I only have reference # as the app was denied. # XXXX</t>
+          <t>Issue: Closing on a mortgage
+Sub-issue: Delays with the closing process
+Complaint: I have a complaint from the credit bureau my ID restoration was hacked and stolen from the data breach attack. I lost my information and contact with account agent. I have a personal workers compensation complaints from the illness. I have been trying to get my insurance renewed with the account litigation on file with the account fraud. I want to pursue with a account take over compromised ID restoration for financial compromise of Government accounts. I have a suspension access of liability insurance dispute from my complaint. I have a email arbitration dispute that involves a error log in of account manager.</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
           <t>Dear [Consumer's Name],
-Thank you for bringing this issue to our attention. We understand your frustration regarding the denial letter and difficulties in obtaining your credit report. Please rest assured that we take these matters seriously. We recommend contacting our customer service team directly with your reference number, and they can assist you in resolving this issue and help you understand your credit status better. Your patience is greatly appreciated. 
+Thank you for reaching out and sharing your concerns regarding the delays in your mortgage closing process. We understand that dealing with identity theft and insurance issues can be incredibly frustrating, and we sincerely apologize for the challenges you’re facing. Please rest assured that we are committed to resolving this matter promptly. We recommend contacting our customer support team directly at [phone number] or [email address] so we can provide you with the personalized assistance you need to navigate these issues effectively.
 Best regards,  
 [Your Name]  
 [Your Position]  
@@ -1636,31 +1637,32 @@
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
     </row>
-    <row r="31" ht="124" customHeight="1">
+    <row r="31" ht="334" customHeight="1">
       <c r="A31" t="n">
         <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>R1ab1fd2a</t>
+          <t>Rd7236e6d</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>Issue: Problem with a company's investigation into an existing problem
-Sub-issue: Was not notified of investigation status or results
-Complaint: PLEASE BLOCKED AND REMOVED. Please expedite the removal of the unauthorized accounts from my credit report at your earliest convenience. I did not initiate or authorize these accounts, and I am unaware of their origins. In accordance with USC 1681g, I am formally requesting their removal within the next 15 days. Enclosed are the pertinent documents for your thorough review and reference.</t>
+          <t>Issue: Took or threatened to take negative or legal action
+Sub-issue: Threatened to arrest you or take you to jail if you do not pay
+Complaint: XXXX I called my XXXX XXXX XXXX and was notified that a third group named Bayou View Solution has purchased my debt phone number XXXX. I had been contacting the older creditor XXXXXXXX XXXX XXXX for several months to update a wrong balance. I recently talked to them. In my past i put in a disputes for records. These peole are targeting covid victims. 
+XXXX I received a no caller ID call someone with the incorrect address claiming to serve me but provided me with the law firm contact XXXX. I called and was placed on a 10 minute hold. He said I was being sued for {$16000.00}. I was in shock knowing my consumer report I first thought it was fraud and Identity Theft. He then came back and said that he was wrong and it was the amount of {$6000.00} same incorrect balance as XXXX XXXX reported same debt which I had mentioned they sold to this group making threats in the middle of the afternoon while I am at work. The male was rude and did not provide me with his name nor allowed me to speak. He then hung up on me. Twice I called back 3 times. To file a complaint. He said let 's talk in court with the papers, I said this is a recorded line and I am asking his name and details about my account. He then said he wants to file a cease and desist. This was an alarm to me and this tactic is not fair. He also said this company had been looking for me but they could not reach me so they are now trying to serve me. He hung up and blocked my number as I asked for account information. I could [...]</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>Acknowledgement: We understand that you are experiencing issues with unauthorized accounts on your credit report and have not received updates regarding the investigation into this matter.  
-Next step: Our team will review the documents you provided and will reach out to you with an update on the status of the investigation within the next 30 days.  
+          <t>Acknowledgement: We understand that you are concerned about being threatened with legal action regarding a debt you believe to be inaccurate and that you experienced rude behavior during your interactions with a debt collection agency.  
+Next step: We will review your complaint and reach out to the relevant department to investigate this matter further within the next seven business days.  
 What we need from you: Nothing at this time.</t>
         </is>
       </c>
